--- a/frontend/public/templates/accounts-import-template.xlsx
+++ b/frontend/public/templates/accounts-import-template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="1" r:id="Re8f9da5f92344278"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账号导入" sheetId="2" r:id="R4582be9cad7540df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="1" r:id="Rf3e992bc7db44f0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账号导入" sheetId="2" r:id="R3cc410c999324eb2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -510,10 +510,10 @@
         <x:v>邮箱</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="C5" s="17" t="str">
-        <x:v>必须唯一，可直接用于登录</x:v>
+        <x:v>与账号名至少填写一个；填写时必须唯一，也可直接用于登录</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
         <x:v>zhangsan@cau.edu.cn</x:v>
@@ -524,10 +524,10 @@
         <x:v>账号名</x:v>
       </x:c>
       <x:c r="B6" s="17" t="str">
-        <x:v>否</x:v>
+        <x:v>条件必填</x:v>
       </x:c>
       <x:c r="C6" s="17" t="str">
-        <x:v>留空时自动使用邮箱，填写时必须唯一</x:v>
+        <x:v>无邮箱时必须填写；有邮箱时可留空并自动使用邮箱</x:v>
       </x:c>
       <x:c r="D6" s="17" t="str">
         <x:v>zhangsan</x:v>
